--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,10 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">
- - L'entrée 'FR-Resultats' est une entrée de type 'organizer' regroupant les types des résultats classés par type d’examens (BIO, IMG, etc…).
- - L'entrée 'FR-Resultats' est une entrée de type 'organizer' regroupant les types des résultats classés par type d’examens (BIO, IMG, etc…).
-</t>
+    <t>FrDiagnosticReportDocument est un profil permettant de regrouper les types des résultats classés par type d’examens (BIO, IMG, etc…).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -489,7 +486,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>Identifiers assigned to this report by the performer or other systems.</t>
@@ -548,7 +545,7 @@
     <t>DiagnosticReport.status</t>
   </si>
   <si>
-    <t>Statut  de l'entrée</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>The status of the diagnostic report.</t>
@@ -623,7 +620,7 @@
 </t>
   </si>
   <si>
-    <t>Type de résultat. Code de l'entrée en LOINC.</t>
+    <t>Type de résultat. Codee n LOINC.</t>
   </si>
   <si>
     <t>A code or name that describes this diagnostic report.</t>
